--- a/prueba.xlsx
+++ b/prueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7693" uniqueCount="1842">
   <si>
     <t>ID</t>
   </si>
@@ -352,18 +352,18 @@
     <t>79802679-3c2e-402f-9570-27c81987edb2</t>
   </si>
   <si>
+    <t>be33406f-11a9-4b39-8055-d84860ed5a59</t>
+  </si>
+  <si>
+    <t>77173356-3661-471c-844e-1dab2ca542a7</t>
+  </si>
+  <si>
     <t>d19134ba-c5d1-4378-95e2-0c64dd97a1ae</t>
   </si>
   <si>
     <t>ffdfa965-3ae1-4975-b3f8-6774da694d44</t>
   </si>
   <si>
-    <t>be33406f-11a9-4b39-8055-d84860ed5a59</t>
-  </si>
-  <si>
-    <t>77173356-3661-471c-844e-1dab2ca542a7</t>
-  </si>
-  <si>
     <t>fa96cdb6-afe4-4c56-95e1-f45e9c49d60a</t>
   </si>
   <si>
@@ -406,27 +406,27 @@
     <t>b68d1a24-8628-4f90-a14c-d23ebc29488b</t>
   </si>
   <si>
+    <t>d8193026-16fc-49c2-87bf-56c6d6b98161</t>
+  </si>
+  <si>
+    <t>09:55:58</t>
+  </si>
+  <si>
+    <t>JOCELYN ÑANCO CALFUQUEO</t>
+  </si>
+  <si>
+    <t>14.140.271-4</t>
+  </si>
+  <si>
+    <t>530a0ffe-8ec6-4a79-ac05-fb687a204510</t>
+  </si>
+  <si>
     <t>c3f466eb-4e77-4990-86fb-f5f6e0c44f9a</t>
   </si>
   <si>
-    <t>09:55:58</t>
-  </si>
-  <si>
-    <t>JOCELYN ÑANCO CALFUQUEO</t>
-  </si>
-  <si>
-    <t>14.140.271-4</t>
-  </si>
-  <si>
     <t>e62d902c-b2a0-4fc2-8158-3daa5c74ad1e</t>
   </si>
   <si>
-    <t>d8193026-16fc-49c2-87bf-56c6d6b98161</t>
-  </si>
-  <si>
-    <t>530a0ffe-8ec6-4a79-ac05-fb687a204510</t>
-  </si>
-  <si>
     <t>a2b04348-6e56-4046-9f8b-7e79d48bb1ad</t>
   </si>
   <si>
@@ -550,39 +550,45 @@
     <t>0f5c5da1-96c3-4b38-8e35-5bb59ca604d5</t>
   </si>
   <si>
+    <t>35710962-fe00-4a88-872e-f444f3e13293</t>
+  </si>
+  <si>
+    <t>10:04:29</t>
+  </si>
+  <si>
+    <t>FRANCISCO HIDALGO PEREZ</t>
+  </si>
+  <si>
+    <t>16.750.544-9</t>
+  </si>
+  <si>
+    <t>0b477e22-e628-4e5f-9af8-078de77cdf65</t>
+  </si>
+  <si>
     <t>047a8a6c-f29d-4038-bc1d-62a9fdd5c436</t>
   </si>
   <si>
-    <t>10:04:29</t>
-  </si>
-  <si>
-    <t>FRANCISCO HIDALGO PEREZ</t>
-  </si>
-  <si>
-    <t>16.750.544-9</t>
-  </si>
-  <si>
     <t>adc9f193-0078-40e2-bcb1-82bc979be5bc</t>
   </si>
   <si>
-    <t>35710962-fe00-4a88-872e-f444f3e13293</t>
-  </si>
-  <si>
-    <t>0b477e22-e628-4e5f-9af8-078de77cdf65</t>
+    <t>0f4ad53a-cd73-40b3-ab97-3900f8ee8424</t>
+  </si>
+  <si>
+    <t>10:05:59</t>
+  </si>
+  <si>
+    <t>Mario Monsálvez Hormazábal</t>
+  </si>
+  <si>
+    <t>22.233.492-6</t>
+  </si>
+  <si>
+    <t>4469dedd-78f0-4f10-995e-8cfe9ab75bbc</t>
   </si>
   <si>
     <t>3315912c-f01f-4fed-80b8-41cc91d4ab15</t>
   </si>
   <si>
-    <t>10:05:59</t>
-  </si>
-  <si>
-    <t>Mario Monsálvez Hormazábal</t>
-  </si>
-  <si>
-    <t>22.233.492-6</t>
-  </si>
-  <si>
     <t>02af8acf-193e-42db-b89c-84556ec34ca5</t>
   </si>
   <si>
@@ -592,12 +598,6 @@
     <t>8801a585-69e6-43e7-bb3d-296ae3f94366</t>
   </si>
   <si>
-    <t>0f4ad53a-cd73-40b3-ab97-3900f8ee8424</t>
-  </si>
-  <si>
-    <t>4469dedd-78f0-4f10-995e-8cfe9ab75bbc</t>
-  </si>
-  <si>
     <t>5fd0ab48-7586-41ca-8264-991d659d04df</t>
   </si>
   <si>
@@ -631,27 +631,27 @@
     <t>892f7095-3373-4f50-927d-6f1add028162</t>
   </si>
   <si>
+    <t>6b8b71fa-7921-481f-8c2d-09458f5d2a48</t>
+  </si>
+  <si>
+    <t>10:12:19</t>
+  </si>
+  <si>
+    <t>carlos tapia</t>
+  </si>
+  <si>
+    <t>12.720.769-0</t>
+  </si>
+  <si>
+    <t>6ed72830-0783-4e86-9fa7-1f3bc38433db</t>
+  </si>
+  <si>
     <t>f1c2c2d2-ed09-4f58-a4ef-a5f08b58554f</t>
   </si>
   <si>
-    <t>10:12:19</t>
-  </si>
-  <si>
-    <t>carlos tapia</t>
-  </si>
-  <si>
-    <t>12.720.769-0</t>
-  </si>
-  <si>
     <t>3bd0ee71-4669-4994-a622-446331115c44</t>
   </si>
   <si>
-    <t>6b8b71fa-7921-481f-8c2d-09458f5d2a48</t>
-  </si>
-  <si>
-    <t>6ed72830-0783-4e86-9fa7-1f3bc38433db</t>
-  </si>
-  <si>
     <t>2ab5af24-5d6a-4e4d-a530-7d2c1cfe5077</t>
   </si>
   <si>
@@ -760,33 +760,33 @@
     <t>19a69790-fc1a-4a8a-b9a4-836be038adbd</t>
   </si>
   <si>
+    <t>ac3c8340-9b20-462a-b63a-9c65890de6b8</t>
+  </si>
+  <si>
+    <t>10:28:34</t>
+  </si>
+  <si>
+    <t>rodrigo araya donoso</t>
+  </si>
+  <si>
+    <t>1.365.520-4</t>
+  </si>
+  <si>
+    <t>8c366d71-7bda-481f-ba2c-5068582fbd44</t>
+  </si>
+  <si>
+    <t>cd81712e-33a1-4e87-a117-05f071c39442</t>
+  </si>
+  <si>
+    <t>db86862c-8caa-444a-bdf6-710632ee48fb</t>
+  </si>
+  <si>
     <t>75e88897-292f-470b-8103-162e0df5d853</t>
   </si>
   <si>
-    <t>10:28:34</t>
-  </si>
-  <si>
-    <t>rodrigo araya donoso</t>
-  </si>
-  <si>
-    <t>1.365.520-4</t>
-  </si>
-  <si>
     <t>2c174cba-2ef5-422c-9303-6b4026439ab8</t>
   </si>
   <si>
-    <t>ac3c8340-9b20-462a-b63a-9c65890de6b8</t>
-  </si>
-  <si>
-    <t>8c366d71-7bda-481f-ba2c-5068582fbd44</t>
-  </si>
-  <si>
-    <t>cd81712e-33a1-4e87-a117-05f071c39442</t>
-  </si>
-  <si>
-    <t>db86862c-8caa-444a-bdf6-710632ee48fb</t>
-  </si>
-  <si>
     <t>e7675868-f823-4e49-8c0d-28a0041df8af</t>
   </si>
   <si>
@@ -1033,21 +1033,21 @@
     <t>85caa2ae-c581-4989-9289-25eb8a25f97e</t>
   </si>
   <si>
+    <t>154b1778-b640-41ff-a995-b40c32545280</t>
+  </si>
+  <si>
+    <t>10:36:24</t>
+  </si>
+  <si>
+    <t>b6f660aa-3999-4ebe-adf0-00899ec373a8</t>
+  </si>
+  <si>
     <t>042846e2-bef7-4a37-a1c3-e4b52a36dc21</t>
   </si>
   <si>
-    <t>10:36:24</t>
-  </si>
-  <si>
     <t>192e66c2-b39c-4c2c-9a74-59a1f1152889</t>
   </si>
   <si>
-    <t>154b1778-b640-41ff-a995-b40c32545280</t>
-  </si>
-  <si>
-    <t>b6f660aa-3999-4ebe-adf0-00899ec373a8</t>
-  </si>
-  <si>
     <t>e96f87ae-8399-44af-89e4-3f4fbd79a7da</t>
   </si>
   <si>
@@ -1111,12 +1111,18 @@
     <t>1e135e6f-75e7-484a-92d2-cae27ab87c2c</t>
   </si>
   <si>
+    <t>fe117bbb-baee-4a98-8397-7d4c48019882</t>
+  </si>
+  <si>
+    <t>10:52:53</t>
+  </si>
+  <si>
+    <t>9fe8c1b4-f7f4-4497-8982-643b80172437</t>
+  </si>
+  <si>
     <t>d8db2fc6-40b3-4afe-9699-67556ca29394</t>
   </si>
   <si>
-    <t>10:52:53</t>
-  </si>
-  <si>
     <t>433a7bd1-4e86-470d-a7e4-1b7eeeda72da</t>
   </si>
   <si>
@@ -1138,12 +1144,6 @@
     <t>da655905-b41f-4423-a09f-41d190844025</t>
   </si>
   <si>
-    <t>fe117bbb-baee-4a98-8397-7d4c48019882</t>
-  </si>
-  <si>
-    <t>9fe8c1b4-f7f4-4497-8982-643b80172437</t>
-  </si>
-  <si>
     <t>11029b4a-27e6-4076-a587-33f151d5b549</t>
   </si>
   <si>
@@ -1273,79 +1273,85 @@
     <t>226dc797-1bb0-4777-9e40-ccb79a1b4c3e</t>
   </si>
   <si>
+    <t>689f9ada-cc01-4989-b1a1-9bf31f5910cb</t>
+  </si>
+  <si>
+    <t>8ba96ded-a543-474d-9fb3-a6a88cad706e</t>
+  </si>
+  <si>
+    <t>4735c8fe-b0cf-4022-b9a7-5d6bb04d5c23</t>
+  </si>
+  <si>
+    <t>ce2f8e55-d015-4420-b57b-ac56de87d8ef</t>
+  </si>
+  <si>
+    <t>413a4960-7f53-4cad-9104-bf60331a65a6</t>
+  </si>
+  <si>
+    <t>91018821-0409-4828-b2ec-933b6351d393</t>
+  </si>
+  <si>
+    <t>41e2a703-66c4-4fa3-b2ba-869aed757662</t>
+  </si>
+  <si>
+    <t>3ed57a68-4bdc-4fd4-b640-941d3e03795f</t>
+  </si>
+  <si>
+    <t>8f321f9b-50cc-4efa-be2b-23133fd56cb5</t>
+  </si>
+  <si>
+    <t>80019534-d072-47c9-b3da-ac0b9dec506b</t>
+  </si>
+  <si>
     <t>734e4c79-a1bc-4cd2-9f08-ed139c79c665</t>
   </si>
   <si>
     <t>7eeaec61-0e40-4aac-9d87-5e54ac771b8e</t>
   </si>
   <si>
-    <t>689f9ada-cc01-4989-b1a1-9bf31f5910cb</t>
-  </si>
-  <si>
-    <t>8ba96ded-a543-474d-9fb3-a6a88cad706e</t>
-  </si>
-  <si>
-    <t>4735c8fe-b0cf-4022-b9a7-5d6bb04d5c23</t>
-  </si>
-  <si>
-    <t>ce2f8e55-d015-4420-b57b-ac56de87d8ef</t>
-  </si>
-  <si>
-    <t>413a4960-7f53-4cad-9104-bf60331a65a6</t>
-  </si>
-  <si>
-    <t>91018821-0409-4828-b2ec-933b6351d393</t>
-  </si>
-  <si>
-    <t>41e2a703-66c4-4fa3-b2ba-869aed757662</t>
-  </si>
-  <si>
-    <t>3ed57a68-4bdc-4fd4-b640-941d3e03795f</t>
-  </si>
-  <si>
-    <t>8f321f9b-50cc-4efa-be2b-23133fd56cb5</t>
-  </si>
-  <si>
-    <t>80019534-d072-47c9-b3da-ac0b9dec506b</t>
-  </si>
-  <si>
     <t>77aeaa9d-12a3-457b-86b2-1ea9d19cabdb</t>
   </si>
   <si>
     <t>871cf11f-bd77-47de-bc85-bcd89c327bcb</t>
   </si>
   <si>
+    <t>c3bf57bd-0dec-4f8a-9f8f-79e9dbf3e6bf</t>
+  </si>
+  <si>
+    <t>9d744c41-2514-4ab3-b6f3-0925ea940354</t>
+  </si>
+  <si>
+    <t>b50d7344-c5be-4e6a-9ba3-09403b3ce876</t>
+  </si>
+  <si>
+    <t>0c4a7b06-175c-4f77-adba-d247845d5d6a</t>
+  </si>
+  <si>
     <t>b11700c1-84a8-4f78-92ff-2b9be5ff8648</t>
   </si>
   <si>
     <t>11e758db-a936-47e6-aa7f-7437ee304ea3</t>
   </si>
   <si>
-    <t>b50d7344-c5be-4e6a-9ba3-09403b3ce876</t>
-  </si>
-  <si>
-    <t>0c4a7b06-175c-4f77-adba-d247845d5d6a</t>
-  </si>
-  <si>
-    <t>c3bf57bd-0dec-4f8a-9f8f-79e9dbf3e6bf</t>
-  </si>
-  <si>
-    <t>9d744c41-2514-4ab3-b6f3-0925ea940354</t>
+    <t>a9402fc4-7dc2-4354-a4b3-2e9233dc15d6</t>
+  </si>
+  <si>
+    <t>11:09:09</t>
+  </si>
+  <si>
+    <t>e497baba-dca9-4c26-a254-417e98979474</t>
   </si>
   <si>
     <t>becf0ace-37b7-4471-a18f-a164f54f0025</t>
   </si>
   <si>
-    <t>11:09:09</t>
-  </si>
-  <si>
     <t>a12277cd-47f3-4e43-a80a-c537a6df9f2e</t>
   </si>
   <si>
-    <t>a9402fc4-7dc2-4354-a4b3-2e9233dc15d6</t>
-  </si>
-  <si>
-    <t>e497baba-dca9-4c26-a254-417e98979474</t>
+    <t>8f9ce2bf-40b6-4be4-b682-31fa0dc60414</t>
+  </si>
+  <si>
+    <t>c24d02ba-2675-4251-b853-6e40bd0311b7</t>
   </si>
   <si>
     <t>99a4c66e-5247-474a-af52-f2cbb6ad2039</t>
@@ -1360,12 +1366,6 @@
     <t>67db6f00-c28d-47d6-814a-cc9af9cfd85d</t>
   </si>
   <si>
-    <t>8f9ce2bf-40b6-4be4-b682-31fa0dc60414</t>
-  </si>
-  <si>
-    <t>c24d02ba-2675-4251-b853-6e40bd0311b7</t>
-  </si>
-  <si>
     <t>5141d56c-c961-45bc-b762-57d401c83fbe</t>
   </si>
   <si>
@@ -1708,16 +1708,22 @@
     <t>e2a175ce-f39b-4cc8-a176-359f2116f4d5</t>
   </si>
   <si>
+    <t>47ddb250-7782-49c5-8c94-1168aa36b611</t>
+  </si>
+  <si>
+    <t>ce541e0f-09f9-48b5-b53b-99395e6c1822</t>
+  </si>
+  <si>
     <t>559ae643-64a9-4066-a270-452272d54716</t>
   </si>
   <si>
     <t>5215930c-d9f5-4902-ad9f-b48da857b580</t>
   </si>
   <si>
-    <t>47ddb250-7782-49c5-8c94-1168aa36b611</t>
-  </si>
-  <si>
-    <t>ce541e0f-09f9-48b5-b53b-99395e6c1822</t>
+    <t>6c8bbef7-9cd5-4411-b9b7-34d776cd17ae</t>
+  </si>
+  <si>
+    <t>faa1ad99-5e0f-4723-866b-bbb89eb49139</t>
   </si>
   <si>
     <t>6425a5ac-19be-4456-9993-fc2bb656928d</t>
@@ -1726,12 +1732,6 @@
     <t>b20b1b9d-d95d-4678-a7c3-ebe9eed6b285</t>
   </si>
   <si>
-    <t>6c8bbef7-9cd5-4411-b9b7-34d776cd17ae</t>
-  </si>
-  <si>
-    <t>faa1ad99-5e0f-4723-866b-bbb89eb49139</t>
-  </si>
-  <si>
     <t>31add93c-70ca-4a5a-901a-47cb92b86815</t>
   </si>
   <si>
@@ -1753,18 +1753,18 @@
     <t>cf365aa1-ec7a-4c3f-aba5-247c321b5f95</t>
   </si>
   <si>
+    <t>410cafce-89f0-4d51-bf2f-14210967a837</t>
+  </si>
+  <si>
+    <t>510da22e-3b3c-4d00-9d82-7acf781470c6</t>
+  </si>
+  <si>
     <t>3e6cb43c-accf-4edb-af28-4c61ef6018fc</t>
   </si>
   <si>
     <t>226015cb-03d0-4dff-b818-23d5fdbbeec0</t>
   </si>
   <si>
-    <t>410cafce-89f0-4d51-bf2f-14210967a837</t>
-  </si>
-  <si>
-    <t>510da22e-3b3c-4d00-9d82-7acf781470c6</t>
-  </si>
-  <si>
     <t>b486edf5-e468-4165-ba59-804504318d77</t>
   </si>
   <si>
@@ -1816,18 +1816,18 @@
     <t>98c33c85-717c-4618-a7b5-3a11ee614a80</t>
   </si>
   <si>
+    <t>8730613e-0ed4-4785-a639-aef4cb593c33</t>
+  </si>
+  <si>
+    <t>2c602798-cc3a-4272-9c99-b073bf2f9ddb</t>
+  </si>
+  <si>
     <t>8938510e-a40d-4e86-b399-204d7e6b2929</t>
   </si>
   <si>
     <t>36ead6cf-2225-4bcb-a1b9-91b00da1619e</t>
   </si>
   <si>
-    <t>8730613e-0ed4-4785-a639-aef4cb593c33</t>
-  </si>
-  <si>
-    <t>2c602798-cc3a-4272-9c99-b073bf2f9ddb</t>
-  </si>
-  <si>
     <t>4a0f777c-b7ec-4f36-b86b-d1aa7877ee10</t>
   </si>
   <si>
@@ -1978,24 +1978,24 @@
     <t>536207da-098c-4092-b37d-c5abeea2bf85</t>
   </si>
   <si>
+    <t>7516347f-c746-4a6f-a49e-1bcd59f77dd6</t>
+  </si>
+  <si>
+    <t>12:10:33</t>
+  </si>
+  <si>
+    <t>13.655.204-K</t>
+  </si>
+  <si>
+    <t>9f790735-d672-4ac6-8e79-fc7a0a91bd7d</t>
+  </si>
+  <si>
     <t>76be765b-cae3-4c47-a5d2-b9fecd8aebf2</t>
   </si>
   <si>
-    <t>12:10:33</t>
-  </si>
-  <si>
-    <t>13.655.204-K</t>
-  </si>
-  <si>
     <t>f49a0042-cdb0-46ed-8a32-95e1e2ef33df</t>
   </si>
   <si>
-    <t>7516347f-c746-4a6f-a49e-1bcd59f77dd6</t>
-  </si>
-  <si>
-    <t>9f790735-d672-4ac6-8e79-fc7a0a91bd7d</t>
-  </si>
-  <si>
     <t>bb5c8021-50f6-4d0c-afac-0bbe62583910</t>
   </si>
   <si>
@@ -2434,24 +2434,24 @@
     <t>2200f070-ebd9-4a8b-812d-8db052485f67</t>
   </si>
   <si>
+    <t>906d44d6-575e-446b-a001-b13e7f3b8d78</t>
+  </si>
+  <si>
+    <t>d55acdac-89b2-4e11-9511-67eeba0e3831</t>
+  </si>
+  <si>
+    <t>8f8c1cbe-4c8d-45c8-a8b9-90a455eae10f</t>
+  </si>
+  <si>
+    <t>ff2edb5e-6039-4f61-9308-cc4b27fbec01</t>
+  </si>
+  <si>
     <t>7bb9e745-9a66-47f5-9be9-e8e65ef8b8a3</t>
   </si>
   <si>
     <t>5cebcc4f-9779-4e58-9644-3f1910be7794</t>
   </si>
   <si>
-    <t>906d44d6-575e-446b-a001-b13e7f3b8d78</t>
-  </si>
-  <si>
-    <t>d55acdac-89b2-4e11-9511-67eeba0e3831</t>
-  </si>
-  <si>
-    <t>8f8c1cbe-4c8d-45c8-a8b9-90a455eae10f</t>
-  </si>
-  <si>
-    <t>ff2edb5e-6039-4f61-9308-cc4b27fbec01</t>
-  </si>
-  <si>
     <t>0fd22a94-fbbd-40a7-8cbe-b3bebcd7dd74</t>
   </si>
   <si>
@@ -2644,66 +2644,66 @@
     <t>55667b57-d4df-4a89-b937-d9084392bb45</t>
   </si>
   <si>
+    <t>9d9477ee-7720-4112-8fe8-5bb6f2a56006</t>
+  </si>
+  <si>
+    <t>12:43:08</t>
+  </si>
+  <si>
+    <t>Mirza Nuñez</t>
+  </si>
+  <si>
+    <t>6.865.539-0</t>
+  </si>
+  <si>
+    <t>7202b759-1cdc-4dbd-91cd-fb765c5e90cd</t>
+  </si>
+  <si>
     <t>057d795a-fd20-4068-9cb9-a649a409bc3c</t>
   </si>
   <si>
-    <t>12:43:08</t>
-  </si>
-  <si>
-    <t>Mirza Nuñez</t>
-  </si>
-  <si>
-    <t>6.865.539-0</t>
-  </si>
-  <si>
     <t>16722040-7701-41fb-bff4-d5153df8fbab</t>
   </si>
   <si>
-    <t>9d9477ee-7720-4112-8fe8-5bb6f2a56006</t>
-  </si>
-  <si>
-    <t>7202b759-1cdc-4dbd-91cd-fb765c5e90cd</t>
+    <t>16d14c62-9d3c-4418-9fa9-2a4481d8a2b1</t>
+  </si>
+  <si>
+    <t>12:43:17</t>
+  </si>
+  <si>
+    <t>YANINA SALAS DELGADILLO</t>
+  </si>
+  <si>
+    <t>14.694.683-6</t>
+  </si>
+  <si>
+    <t>0dafc5e1-3bd9-4207-98e1-363d7eff429e</t>
+  </si>
+  <si>
+    <t>31fe8198-0ab5-469a-96f6-34a6436acf4c</t>
+  </si>
+  <si>
+    <t>8e8699ff-5486-4235-ad5c-0b20269ca312</t>
   </si>
   <si>
     <t>9f03ec15-da5c-4287-82ca-f32b08c4ec56</t>
   </si>
   <si>
-    <t>12:43:17</t>
-  </si>
-  <si>
-    <t>YANINA SALAS DELGADILLO</t>
-  </si>
-  <si>
-    <t>14.694.683-6</t>
-  </si>
-  <si>
     <t>ed661621-3402-49cb-a82c-7d96e89c0dda</t>
   </si>
   <si>
+    <t>cc27b8f8-2ac9-4fe2-9a48-a1bf012a89ec</t>
+  </si>
+  <si>
+    <t>a969dfb5-9ccd-4189-9462-dfdffaddf207</t>
+  </si>
+  <si>
     <t>f37ae4cf-9b70-41dd-a048-9a85e283c23e</t>
   </si>
   <si>
     <t>1378d083-b536-469f-b567-d9a85928db6a</t>
   </si>
   <si>
-    <t>cc27b8f8-2ac9-4fe2-9a48-a1bf012a89ec</t>
-  </si>
-  <si>
-    <t>a969dfb5-9ccd-4189-9462-dfdffaddf207</t>
-  </si>
-  <si>
-    <t>16d14c62-9d3c-4418-9fa9-2a4481d8a2b1</t>
-  </si>
-  <si>
-    <t>0dafc5e1-3bd9-4207-98e1-363d7eff429e</t>
-  </si>
-  <si>
-    <t>31fe8198-0ab5-469a-96f6-34a6436acf4c</t>
-  </si>
-  <si>
-    <t>8e8699ff-5486-4235-ad5c-0b20269ca312</t>
-  </si>
-  <si>
     <t>71189e27-9f90-4929-b499-3e7a7208420f</t>
   </si>
   <si>
@@ -2755,21 +2755,21 @@
     <t>35ae2177-c82c-4ee1-935b-bbe1f504a0fa</t>
   </si>
   <si>
+    <t>92e4e095-db97-4335-8aff-60f9eb2bc214</t>
+  </si>
+  <si>
+    <t>12:55:23</t>
+  </si>
+  <si>
+    <t>8fd4ab40-02f7-4dbd-8841-34ec275d7910</t>
+  </si>
+  <si>
     <t>e907bfef-ecdd-4b46-99c5-d5b5a0d2e27e</t>
   </si>
   <si>
-    <t>12:55:23</t>
-  </si>
-  <si>
     <t>e4e35d32-3846-41cf-9cc9-ed31c25c9ca9</t>
   </si>
   <si>
-    <t>92e4e095-db97-4335-8aff-60f9eb2bc214</t>
-  </si>
-  <si>
-    <t>8fd4ab40-02f7-4dbd-8841-34ec275d7910</t>
-  </si>
-  <si>
     <t>37f08062-78ca-4fac-9373-97610ac32ff7</t>
   </si>
   <si>
@@ -2932,36 +2932,36 @@
     <t>8095f914-c2c5-40e0-90b8-dfec7e7f8b92</t>
   </si>
   <si>
+    <t>c448a25a-0d93-4b79-8532-d8b8095d99e4</t>
+  </si>
+  <si>
+    <t>ed4ddd70-5d43-4ed9-9512-57c19df7bd4b</t>
+  </si>
+  <si>
+    <t>15d7817d-b5d9-4106-b872-415cf2997f54</t>
+  </si>
+  <si>
+    <t>90edaf8f-7b46-45b0-95f2-e5e22bcf0086</t>
+  </si>
+  <si>
+    <t>632f9b9b-cca6-4778-9e1a-1967c06dadd4</t>
+  </si>
+  <si>
+    <t>3949490c-b7e2-4585-a305-ddfabc8aba9c</t>
+  </si>
+  <si>
+    <t>49567251-5b07-43e1-a2b9-1abc02e9a152</t>
+  </si>
+  <si>
+    <t>3d13f9c1-e191-4ec8-a837-eb56bc178736</t>
+  </si>
+  <si>
     <t>ef52c66f-6a6d-48ca-842c-467c516eb6a5</t>
   </si>
   <si>
     <t>d2c548e5-a83f-4d50-b75b-4b1dfe36217c</t>
   </si>
   <si>
-    <t>c448a25a-0d93-4b79-8532-d8b8095d99e4</t>
-  </si>
-  <si>
-    <t>ed4ddd70-5d43-4ed9-9512-57c19df7bd4b</t>
-  </si>
-  <si>
-    <t>15d7817d-b5d9-4106-b872-415cf2997f54</t>
-  </si>
-  <si>
-    <t>90edaf8f-7b46-45b0-95f2-e5e22bcf0086</t>
-  </si>
-  <si>
-    <t>632f9b9b-cca6-4778-9e1a-1967c06dadd4</t>
-  </si>
-  <si>
-    <t>3949490c-b7e2-4585-a305-ddfabc8aba9c</t>
-  </si>
-  <si>
-    <t>49567251-5b07-43e1-a2b9-1abc02e9a152</t>
-  </si>
-  <si>
-    <t>3d13f9c1-e191-4ec8-a837-eb56bc178736</t>
-  </si>
-  <si>
     <t>fa076e3d-3091-4142-9265-a039a7170062</t>
   </si>
   <si>
@@ -3148,6 +3148,12 @@
     <t>e617b635-79a3-46c8-882d-ffb73fe12436</t>
   </si>
   <si>
+    <t>933e45ba-d1e2-4ebc-99f3-31b1641cadc9</t>
+  </si>
+  <si>
+    <t>cd80173e-e002-49d1-b130-a6af56e3ad89</t>
+  </si>
+  <si>
     <t>b2f6ab1a-c325-4e60-bf30-58249e49060e</t>
   </si>
   <si>
@@ -3160,12 +3166,6 @@
     <t>2b0dad60-ddaf-4af8-9e71-9ce8289a689e</t>
   </si>
   <si>
-    <t>933e45ba-d1e2-4ebc-99f3-31b1641cadc9</t>
-  </si>
-  <si>
-    <t>cd80173e-e002-49d1-b130-a6af56e3ad89</t>
-  </si>
-  <si>
     <t>6eb1ba74-4553-4a63-92cc-66d837004a7e</t>
   </si>
   <si>
@@ -3775,18 +3775,18 @@
     <t>899426b3-d7ce-4ea5-914a-f2bc972cb85a</t>
   </si>
   <si>
+    <t>c00aff3d-3a2b-4b51-89f6-69ce20bad697</t>
+  </si>
+  <si>
+    <t>bc872229-14a5-41ca-82f1-def883ed8a29</t>
+  </si>
+  <si>
     <t>ecdeb891-245c-4111-af9b-0122f23311ed</t>
   </si>
   <si>
     <t>5272d1b1-118d-4b7b-915b-a21d8ecbcebe</t>
   </si>
   <si>
-    <t>c00aff3d-3a2b-4b51-89f6-69ce20bad697</t>
-  </si>
-  <si>
-    <t>bc872229-14a5-41ca-82f1-def883ed8a29</t>
-  </si>
-  <si>
     <t>c0f93df5-9800-4671-b4d7-cb2ea1f8c0ab</t>
   </si>
   <si>
@@ -3847,46 +3847,70 @@
     <t>5d85e7d0-cfa1-4e72-99ac-daf8b98be8d5</t>
   </si>
   <si>
+    <t>513683cf-061e-41dc-8f93-8f94f9319497</t>
+  </si>
+  <si>
+    <t>12ef49ce-efe8-4f31-b169-b58276b5d517</t>
+  </si>
+  <si>
+    <t>38228e65-970d-4b68-aa1b-2c5dd8a91da5</t>
+  </si>
+  <si>
+    <t>611495a8-622c-46ee-8925-5086abc311f1</t>
+  </si>
+  <si>
+    <t>02d9abe0-9b2c-447d-8050-2bd6ac8f8efa</t>
+  </si>
+  <si>
+    <t>b234a737-f35f-4716-93b3-cbccdeb4c6c3</t>
+  </si>
+  <si>
+    <t>0bf09a2a-2805-493e-bd6b-d52bbef5d1c9</t>
+  </si>
+  <si>
+    <t>3319b848-017b-443a-801e-afad28855911</t>
+  </si>
+  <si>
+    <t>2c661f49-805d-4bcf-a869-b32c38fda345</t>
+  </si>
+  <si>
+    <t>104c45f2-319c-4e3d-9096-53eafab8a962</t>
+  </si>
+  <si>
+    <t>d736ced0-37ea-4731-9ada-98c012342ec7</t>
+  </si>
+  <si>
+    <t>cef0af04-2628-47e9-91e1-7726aaff3df4</t>
+  </si>
+  <si>
     <t>71619b90-c79e-45bf-a549-627d705baaa6</t>
   </si>
   <si>
     <t>72de4f5b-3056-4568-b52f-7e236fc92630</t>
   </si>
   <si>
-    <t>513683cf-061e-41dc-8f93-8f94f9319497</t>
-  </si>
-  <si>
-    <t>12ef49ce-efe8-4f31-b169-b58276b5d517</t>
-  </si>
-  <si>
-    <t>02d9abe0-9b2c-447d-8050-2bd6ac8f8efa</t>
-  </si>
-  <si>
-    <t>b234a737-f35f-4716-93b3-cbccdeb4c6c3</t>
-  </si>
-  <si>
-    <t>0bf09a2a-2805-493e-bd6b-d52bbef5d1c9</t>
-  </si>
-  <si>
-    <t>3319b848-017b-443a-801e-afad28855911</t>
-  </si>
-  <si>
-    <t>38228e65-970d-4b68-aa1b-2c5dd8a91da5</t>
-  </si>
-  <si>
-    <t>611495a8-622c-46ee-8925-5086abc311f1</t>
-  </si>
-  <si>
-    <t>2c661f49-805d-4bcf-a869-b32c38fda345</t>
-  </si>
-  <si>
-    <t>104c45f2-319c-4e3d-9096-53eafab8a962</t>
-  </si>
-  <si>
-    <t>d736ced0-37ea-4731-9ada-98c012342ec7</t>
-  </si>
-  <si>
-    <t>cef0af04-2628-47e9-91e1-7726aaff3df4</t>
+    <t>874ff75b-0024-4fe2-a19f-062a0fa20516</t>
+  </si>
+  <si>
+    <t>ad463ddd-eff0-4b14-83d9-46450191af75</t>
+  </si>
+  <si>
+    <t>812a0050-8c5e-4687-94ca-5b62f280bd73</t>
+  </si>
+  <si>
+    <t>69495346-cab3-4ffd-a57e-8c23c4c56cad</t>
+  </si>
+  <si>
+    <t>9e9ac575-d891-4edf-b629-aa4d73db794d</t>
+  </si>
+  <si>
+    <t>69a7fc72-2bb3-4e00-b475-e9e77f21377f</t>
+  </si>
+  <si>
+    <t>94f878ea-b528-4807-a91f-13939cf9cf24</t>
+  </si>
+  <si>
+    <t>f3de2f8e-df07-4394-96c0-aa198f53e744</t>
   </si>
   <si>
     <t>e87a43c4-d553-4179-ac11-88c799140966</t>
@@ -3895,30 +3919,6 @@
     <t>2c4a0448-ce8e-4793-9942-068d2e396834</t>
   </si>
   <si>
-    <t>9e9ac575-d891-4edf-b629-aa4d73db794d</t>
-  </si>
-  <si>
-    <t>69a7fc72-2bb3-4e00-b475-e9e77f21377f</t>
-  </si>
-  <si>
-    <t>812a0050-8c5e-4687-94ca-5b62f280bd73</t>
-  </si>
-  <si>
-    <t>69495346-cab3-4ffd-a57e-8c23c4c56cad</t>
-  </si>
-  <si>
-    <t>874ff75b-0024-4fe2-a19f-062a0fa20516</t>
-  </si>
-  <si>
-    <t>ad463ddd-eff0-4b14-83d9-46450191af75</t>
-  </si>
-  <si>
-    <t>94f878ea-b528-4807-a91f-13939cf9cf24</t>
-  </si>
-  <si>
-    <t>f3de2f8e-df07-4394-96c0-aa198f53e744</t>
-  </si>
-  <si>
     <t>fc0940f2-0753-4ef1-a8c4-5dd815fef367</t>
   </si>
   <si>
@@ -4021,6 +4021,42 @@
     <t>71d86caa-7e74-4799-9eb8-ab853205430d</t>
   </si>
   <si>
+    <t>2726423a-6a56-42d5-a634-0d33c532aa6d</t>
+  </si>
+  <si>
+    <t>7f245d76-cb7e-41cc-8236-62965050928f</t>
+  </si>
+  <si>
+    <t>68d5e2da-2bb5-41c0-8c5b-31712ecfffca</t>
+  </si>
+  <si>
+    <t>1d537db0-b8c0-4cc6-89ee-d0b1d8eaeca0</t>
+  </si>
+  <si>
+    <t>561e82cc-2916-432b-b21a-efbf0482bcfc</t>
+  </si>
+  <si>
+    <t>969f9e9d-2595-4af1-bba4-4274ee5c0cfd</t>
+  </si>
+  <si>
+    <t>a37e0d17-53dd-4c53-a952-23d00cc11438</t>
+  </si>
+  <si>
+    <t>ef512de5-fe99-45f8-bd0d-374cacfe1563</t>
+  </si>
+  <si>
+    <t>8aa20b8c-3879-4397-8f97-efa2b017a9b2</t>
+  </si>
+  <si>
+    <t>aecb58ee-c432-4bd9-9753-66f2a3b7e4b6</t>
+  </si>
+  <si>
+    <t>7468eb84-d434-4f05-9a36-ca57ae87e555</t>
+  </si>
+  <si>
+    <t>7c555afe-8568-4835-a9ad-bf5514607d10</t>
+  </si>
+  <si>
     <t>cae7ef36-925e-43e8-8a40-1d88d0b9612f</t>
   </si>
   <si>
@@ -4033,57 +4069,51 @@
     <t>e5cefcb4-2c8e-48d0-80e5-fa5dda2c2220</t>
   </si>
   <si>
-    <t>8aa20b8c-3879-4397-8f97-efa2b017a9b2</t>
-  </si>
-  <si>
-    <t>aecb58ee-c432-4bd9-9753-66f2a3b7e4b6</t>
-  </si>
-  <si>
-    <t>a37e0d17-53dd-4c53-a952-23d00cc11438</t>
-  </si>
-  <si>
-    <t>ef512de5-fe99-45f8-bd0d-374cacfe1563</t>
-  </si>
-  <si>
-    <t>2726423a-6a56-42d5-a634-0d33c532aa6d</t>
-  </si>
-  <si>
-    <t>7f245d76-cb7e-41cc-8236-62965050928f</t>
-  </si>
-  <si>
-    <t>68d5e2da-2bb5-41c0-8c5b-31712ecfffca</t>
-  </si>
-  <si>
-    <t>1d537db0-b8c0-4cc6-89ee-d0b1d8eaeca0</t>
-  </si>
-  <si>
-    <t>7468eb84-d434-4f05-9a36-ca57ae87e555</t>
-  </si>
-  <si>
-    <t>7c555afe-8568-4835-a9ad-bf5514607d10</t>
-  </si>
-  <si>
-    <t>561e82cc-2916-432b-b21a-efbf0482bcfc</t>
-  </si>
-  <si>
-    <t>969f9e9d-2595-4af1-bba4-4274ee5c0cfd</t>
+    <t>d8ccdb91-2a6f-428f-98b0-94f8c346cb29</t>
+  </si>
+  <si>
+    <t>17:07:44</t>
+  </si>
+  <si>
+    <t>Fabio Largacha</t>
+  </si>
+  <si>
+    <t>24.681.353-1</t>
+  </si>
+  <si>
+    <t>aef3493d-04e5-4a8f-a166-1aaef12c2628</t>
+  </si>
+  <si>
+    <t>d3590e7a-73ea-4b4c-a660-5e127d276aed</t>
+  </si>
+  <si>
+    <t>34e64e68-6c0c-4764-90b7-86a7bc1ee9ab</t>
+  </si>
+  <si>
+    <t>d4d1fa53-7f76-4818-bb26-c5609b5daafb</t>
+  </si>
+  <si>
+    <t>a74c3d55-8ae0-4347-acbf-d65e85212634</t>
   </si>
   <si>
     <t>759edbfc-ce31-499d-9cf8-f45b4c4b6134</t>
   </si>
   <si>
-    <t>17:07:44</t>
-  </si>
-  <si>
-    <t>Fabio Largacha</t>
-  </si>
-  <si>
-    <t>24.681.353-1</t>
-  </si>
-  <si>
     <t>80721f0b-3d3d-46b9-970a-a82cef1fa4fe</t>
   </si>
   <si>
+    <t>84faa2b0-0d2f-41da-a71f-80ee00b60453</t>
+  </si>
+  <si>
+    <t>9524da51-86d4-4f6d-bd9b-a3464776c8c3</t>
+  </si>
+  <si>
+    <t>a093fcab-5c6f-46b0-aa2c-8eda314146d4</t>
+  </si>
+  <si>
+    <t>53f74433-cffd-41f3-9fa0-541f9f704aa4</t>
+  </si>
+  <si>
     <t>6228eecd-8593-49f8-8b59-901f3497a689</t>
   </si>
   <si>
@@ -4102,36 +4132,6 @@
     <t>88956692-77d5-489e-9e71-1873c31d5347</t>
   </si>
   <si>
-    <t>a093fcab-5c6f-46b0-aa2c-8eda314146d4</t>
-  </si>
-  <si>
-    <t>53f74433-cffd-41f3-9fa0-541f9f704aa4</t>
-  </si>
-  <si>
-    <t>84faa2b0-0d2f-41da-a71f-80ee00b60453</t>
-  </si>
-  <si>
-    <t>9524da51-86d4-4f6d-bd9b-a3464776c8c3</t>
-  </si>
-  <si>
-    <t>d3590e7a-73ea-4b4c-a660-5e127d276aed</t>
-  </si>
-  <si>
-    <t>34e64e68-6c0c-4764-90b7-86a7bc1ee9ab</t>
-  </si>
-  <si>
-    <t>d4d1fa53-7f76-4818-bb26-c5609b5daafb</t>
-  </si>
-  <si>
-    <t>a74c3d55-8ae0-4347-acbf-d65e85212634</t>
-  </si>
-  <si>
-    <t>d8ccdb91-2a6f-428f-98b0-94f8c346cb29</t>
-  </si>
-  <si>
-    <t>aef3493d-04e5-4a8f-a166-1aaef12c2628</t>
-  </si>
-  <si>
     <t>f5848eb1-700c-4068-aa6e-99a8135813bd</t>
   </si>
   <si>
@@ -4171,33 +4171,33 @@
     <t>0ccff514-567b-4312-9f25-8d8b0a742269</t>
   </si>
   <si>
+    <t>e00ec8c8-4838-4565-9639-abd4860d1721</t>
+  </si>
+  <si>
+    <t>17:08:49</t>
+  </si>
+  <si>
+    <t>Pia Celeste Leiva Rocco</t>
+  </si>
+  <si>
+    <t>27.016.497-8</t>
+  </si>
+  <si>
+    <t>a81bea52-201a-4ebc-a261-ecca450be77c</t>
+  </si>
+  <si>
+    <t>c13dc72d-66b8-4c6f-9831-4f8a13c1b399</t>
+  </si>
+  <si>
+    <t>fcf63486-1ab4-4681-913d-d60daebbbae9</t>
+  </si>
+  <si>
     <t>8d3ef0b4-7c6f-453b-a230-5bb1dbba3388</t>
   </si>
   <si>
-    <t>17:08:49</t>
-  </si>
-  <si>
-    <t>Pia Celeste Leiva Rocco</t>
-  </si>
-  <si>
-    <t>27.016.497-8</t>
-  </si>
-  <si>
     <t>efc7b601-f5cc-42f5-9705-0eaabeae08c3</t>
   </si>
   <si>
-    <t>e00ec8c8-4838-4565-9639-abd4860d1721</t>
-  </si>
-  <si>
-    <t>a81bea52-201a-4ebc-a261-ecca450be77c</t>
-  </si>
-  <si>
-    <t>c13dc72d-66b8-4c6f-9831-4f8a13c1b399</t>
-  </si>
-  <si>
-    <t>fcf63486-1ab4-4681-913d-d60daebbbae9</t>
-  </si>
-  <si>
     <t>5f988f94-4baa-4d43-99e7-bb79cb56254d</t>
   </si>
   <si>
@@ -4243,24 +4243,24 @@
     <t>3272d269-5273-4e60-a927-10fe741b14e4</t>
   </si>
   <si>
+    <t>91c4f236-de76-4617-aa74-1cba5314f696</t>
+  </si>
+  <si>
+    <t>96735f66-9356-4720-9525-1a0218177427</t>
+  </si>
+  <si>
+    <t>78938cfe-70af-4ece-beb0-0446f9dd7b76</t>
+  </si>
+  <si>
+    <t>befaf857-227b-4c6f-9c8d-3059ab2b20d2</t>
+  </si>
+  <si>
     <t>eb8a6593-8a50-4d00-b70f-8c878ca68b6d</t>
   </si>
   <si>
     <t>d0706d43-7927-4cca-8740-733dbd11c449</t>
   </si>
   <si>
-    <t>91c4f236-de76-4617-aa74-1cba5314f696</t>
-  </si>
-  <si>
-    <t>96735f66-9356-4720-9525-1a0218177427</t>
-  </si>
-  <si>
-    <t>78938cfe-70af-4ece-beb0-0446f9dd7b76</t>
-  </si>
-  <si>
-    <t>befaf857-227b-4c6f-9c8d-3059ab2b20d2</t>
-  </si>
-  <si>
     <t>acdfd044-2315-4dba-9d70-2ebf9f05f67c</t>
   </si>
   <si>
@@ -4291,18 +4291,18 @@
     <t>fb0e4d81-c7d7-4ef2-bf49-af097e59ea93</t>
   </si>
   <si>
+    <t>d2bce46c-78c6-4b03-8308-6eb60bbf40f3</t>
+  </si>
+  <si>
+    <t>ab85cca0-2688-4e04-b498-a3aeef22e651</t>
+  </si>
+  <si>
     <t>a491dbd3-8003-447c-b29c-e75072dc2f8e</t>
   </si>
   <si>
     <t>64f3b5f9-21ee-4d41-bd72-257110050165</t>
   </si>
   <si>
-    <t>d2bce46c-78c6-4b03-8308-6eb60bbf40f3</t>
-  </si>
-  <si>
-    <t>ab85cca0-2688-4e04-b498-a3aeef22e651</t>
-  </si>
-  <si>
     <t>6d322715-2f6b-4223-8345-4eec1449a542</t>
   </si>
   <si>
@@ -4324,18 +4324,18 @@
     <t>439def29-f626-4525-a9d4-707d3fdfedd6</t>
   </si>
   <si>
+    <t>db27f5f9-daad-4806-b5be-5f137ecb5e05</t>
+  </si>
+  <si>
+    <t>3ec0cb56-bb47-4f1c-a407-4ab3fbabf8bc</t>
+  </si>
+  <si>
     <t>c24f4dbc-ff7f-4f8e-abe8-70a4de7daea4</t>
   </si>
   <si>
     <t>56466edb-281c-4c72-8a31-c21982e8517e</t>
   </si>
   <si>
-    <t>db27f5f9-daad-4806-b5be-5f137ecb5e05</t>
-  </si>
-  <si>
-    <t>3ec0cb56-bb47-4f1c-a407-4ab3fbabf8bc</t>
-  </si>
-  <si>
     <t>d6e5bd47-c21b-4658-834d-a360a1e525dc</t>
   </si>
   <si>
@@ -4441,6 +4441,12 @@
     <t>82b33e0f-9c8d-40dd-924e-f4c34a3fa36b</t>
   </si>
   <si>
+    <t>74fc4428-5c2d-4881-aebf-8f6e21ac0e41</t>
+  </si>
+  <si>
+    <t>8972621c-b3f9-4f6b-80a6-95a0f35bf018</t>
+  </si>
+  <si>
     <t>b4450b7f-664e-4b59-9b5e-a33ebc104463</t>
   </si>
   <si>
@@ -4453,12 +4459,6 @@
     <t>bfc1c6a1-349b-4112-b635-adcdc84d49cd</t>
   </si>
   <si>
-    <t>74fc4428-5c2d-4881-aebf-8f6e21ac0e41</t>
-  </si>
-  <si>
-    <t>8972621c-b3f9-4f6b-80a6-95a0f35bf018</t>
-  </si>
-  <si>
     <t>65a30ed8-66d6-4aca-9066-4bcaf989a7c1</t>
   </si>
   <si>
@@ -4525,42 +4525,54 @@
     <t>09208ff5-9ded-481f-b29a-c66cbe2594ba</t>
   </si>
   <si>
+    <t>58ce402b-4d50-4138-b21f-bb7fcb1e0976</t>
+  </si>
+  <si>
+    <t>971e4aa1-d42e-438b-8dbe-4413b14aef27</t>
+  </si>
+  <si>
     <t>60f179a2-fbd1-49d0-87de-3b3be06b3b8f</t>
   </si>
   <si>
     <t>4f64f18d-b402-416e-94ac-b1788c898cb7</t>
   </si>
   <si>
-    <t>58ce402b-4d50-4138-b21f-bb7fcb1e0976</t>
-  </si>
-  <si>
-    <t>971e4aa1-d42e-438b-8dbe-4413b14aef27</t>
-  </si>
-  <si>
     <t>38dd7572-797e-4e18-bb10-803774df3b36</t>
   </si>
   <si>
     <t>89f59590-d8f1-4c91-98be-cf9e09575857</t>
   </si>
   <si>
+    <t>0e971eeb-da32-404c-8118-a7d742dca6fa</t>
+  </si>
+  <si>
+    <t>daabd796-4d6d-4b25-8cc4-91227506ec50</t>
+  </si>
+  <si>
     <t>31dd8641-4f60-40af-954e-d8a69574ecb4</t>
   </si>
   <si>
     <t>c1eef7a4-f6e1-42ec-a1e5-95475637f0de</t>
   </si>
   <si>
-    <t>0e971eeb-da32-404c-8118-a7d742dca6fa</t>
-  </si>
-  <si>
-    <t>daabd796-4d6d-4b25-8cc4-91227506ec50</t>
+    <t>2febe2fd-30e0-4560-9f9e-95a8d1258cab</t>
+  </si>
+  <si>
+    <t>17:56:29</t>
+  </si>
+  <si>
+    <t>8b8eb969-166b-4a40-9424-33e6c6cb523d</t>
+  </si>
+  <si>
+    <t>183e51a3-df8b-4445-bf19-cdf107c57b0b</t>
+  </si>
+  <si>
+    <t>cdfaa238-304f-4335-86b9-0fcd0425292c</t>
   </si>
   <si>
     <t>0f9f7572-6135-4905-b4be-ccd09a5a710e</t>
   </si>
   <si>
-    <t>17:56:29</t>
-  </si>
-  <si>
     <t>ed3ae443-6a5a-48a6-b6c2-8070e93b7476</t>
   </si>
   <si>
@@ -4570,16 +4582,10 @@
     <t>d10fe9a3-e5ce-4105-bbdb-7d777186ec78</t>
   </si>
   <si>
-    <t>2febe2fd-30e0-4560-9f9e-95a8d1258cab</t>
-  </si>
-  <si>
-    <t>8b8eb969-166b-4a40-9424-33e6c6cb523d</t>
-  </si>
-  <si>
-    <t>183e51a3-df8b-4445-bf19-cdf107c57b0b</t>
-  </si>
-  <si>
-    <t>cdfaa238-304f-4335-86b9-0fcd0425292c</t>
+    <t>4259e132-3135-4002-940e-d088c291d59b</t>
+  </si>
+  <si>
+    <t>a03319c4-decf-4be4-ad7c-3ba2b4d8b137</t>
   </si>
   <si>
     <t>54647ccf-76fa-4052-b9f5-8e04b4a321cc</t>
@@ -4588,10 +4594,16 @@
     <t>21d09ea0-4ef2-47af-abe8-3b6eab412c2d</t>
   </si>
   <si>
-    <t>4259e132-3135-4002-940e-d088c291d59b</t>
-  </si>
-  <si>
-    <t>a03319c4-decf-4be4-ad7c-3ba2b4d8b137</t>
+    <t>beb219ac-e0a3-4606-8f99-efa24b0e927e</t>
+  </si>
+  <si>
+    <t>2180185b-e270-4fdf-a0b7-3c12a5b1ce2a</t>
+  </si>
+  <si>
+    <t>aca1c349-0557-4adc-a429-2dcf69e0102c</t>
+  </si>
+  <si>
+    <t>915f4e19-1e40-4986-9cd4-c1e69e3d81cc</t>
   </si>
   <si>
     <t>739d087c-4fb3-4820-88cb-d33ddc4caa9e</t>
@@ -4600,24 +4612,12 @@
     <t>a250ab46-9810-4550-b98d-44e86effe1d1</t>
   </si>
   <si>
-    <t>beb219ac-e0a3-4606-8f99-efa24b0e927e</t>
-  </si>
-  <si>
-    <t>2180185b-e270-4fdf-a0b7-3c12a5b1ce2a</t>
-  </si>
-  <si>
     <t>ef2044ee-fd75-4ab5-b68c-7a77402f6697</t>
   </si>
   <si>
     <t>bdaf895b-6e0c-46a5-8f0f-4f91801b3a73</t>
   </si>
   <si>
-    <t>aca1c349-0557-4adc-a429-2dcf69e0102c</t>
-  </si>
-  <si>
-    <t>915f4e19-1e40-4986-9cd4-c1e69e3d81cc</t>
-  </si>
-  <si>
     <t>c401265a-356f-47fb-9509-141ca3b81960</t>
   </si>
   <si>
@@ -4669,28 +4669,46 @@
     <t>e22e3012-9e8e-4280-b376-f8719b96ebb5</t>
   </si>
   <si>
+    <t>8e577127-1a01-4019-bbc1-655b3d953201</t>
+  </si>
+  <si>
+    <t>c971a322-0c20-429b-91fd-ea0faf0cf663</t>
+  </si>
+  <si>
+    <t>d5579bbd-0925-4bcc-b0a6-f41a05f83de4</t>
+  </si>
+  <si>
+    <t>0c4b6d5e-4dbc-465f-b7b8-7c4363aabaa2</t>
+  </si>
+  <si>
+    <t>d62d8791-bb5d-435d-9895-4b215e4085e0</t>
+  </si>
+  <si>
+    <t>3229b99c-5808-4c82-b204-b35edc4641b7</t>
+  </si>
+  <si>
     <t>a8b813c2-4664-49af-bab7-8053837b8cf0</t>
   </si>
   <si>
     <t>ab6aa866-6d3d-4c38-a7a0-4ecf5b49b1b7</t>
   </si>
   <si>
-    <t>8e577127-1a01-4019-bbc1-655b3d953201</t>
-  </si>
-  <si>
-    <t>c971a322-0c20-429b-91fd-ea0faf0cf663</t>
-  </si>
-  <si>
-    <t>d5579bbd-0925-4bcc-b0a6-f41a05f83de4</t>
-  </si>
-  <si>
-    <t>0c4b6d5e-4dbc-465f-b7b8-7c4363aabaa2</t>
-  </si>
-  <si>
-    <t>d62d8791-bb5d-435d-9895-4b215e4085e0</t>
-  </si>
-  <si>
-    <t>3229b99c-5808-4c82-b204-b35edc4641b7</t>
+    <t>32553f23-4469-4756-a850-3a2600a56b0c</t>
+  </si>
+  <si>
+    <t>c11aeb5f-1dba-407e-ad14-51d0067d0fd1</t>
+  </si>
+  <si>
+    <t>4bdf87df-2792-4d75-bd5e-ad00f26065e3</t>
+  </si>
+  <si>
+    <t>1c3c2da9-8cb3-48e5-b9a0-c501b751d6ea</t>
+  </si>
+  <si>
+    <t>fc9a5fd6-11cd-406d-bd49-04cfd0bb68bf</t>
+  </si>
+  <si>
+    <t>4f2f0c99-179e-47c5-8ce4-03e0201ce50d</t>
   </si>
   <si>
     <t>f953a039-ab99-4500-a1ee-505e1e56edcc</t>
@@ -4699,39 +4717,21 @@
     <t>f38b7b9d-9277-4bfc-9881-298cc2ecd96b</t>
   </si>
   <si>
-    <t>32553f23-4469-4756-a850-3a2600a56b0c</t>
-  </si>
-  <si>
-    <t>c11aeb5f-1dba-407e-ad14-51d0067d0fd1</t>
-  </si>
-  <si>
-    <t>4bdf87df-2792-4d75-bd5e-ad00f26065e3</t>
-  </si>
-  <si>
-    <t>1c3c2da9-8cb3-48e5-b9a0-c501b751d6ea</t>
-  </si>
-  <si>
-    <t>fc9a5fd6-11cd-406d-bd49-04cfd0bb68bf</t>
-  </si>
-  <si>
-    <t>4f2f0c99-179e-47c5-8ce4-03e0201ce50d</t>
+    <t>558b825c-bf77-4274-bbec-c7368b314425</t>
+  </si>
+  <si>
+    <t>18:09:00</t>
+  </si>
+  <si>
+    <t>772df6e0-2335-411a-967a-c703a93587bc</t>
   </si>
   <si>
     <t>53099148-48ad-4771-b3a4-68818495bb44</t>
   </si>
   <si>
-    <t>18:09:00</t>
-  </si>
-  <si>
     <t>b2fe05b7-895f-40c2-9a19-965124cb2901</t>
   </si>
   <si>
-    <t>558b825c-bf77-4274-bbec-c7368b314425</t>
-  </si>
-  <si>
-    <t>772df6e0-2335-411a-967a-c703a93587bc</t>
-  </si>
-  <si>
     <t>12fa5215-d262-47df-bdec-cd252b802008</t>
   </si>
   <si>
@@ -4756,82 +4756,88 @@
     <t>d3da7e68-eeb8-4f70-be07-e4ce6f620729</t>
   </si>
   <si>
+    <t>79e0a58a-afc4-48fd-8949-f8a29b6c542e</t>
+  </si>
+  <si>
+    <t>18:12:56</t>
+  </si>
+  <si>
+    <t>MACARENa CATALAN BENITEZ</t>
+  </si>
+  <si>
+    <t>17.229.411-1</t>
+  </si>
+  <si>
+    <t>b96339ce-d0f1-4fac-b32b-66d13f0bf7a7</t>
+  </si>
+  <si>
     <t>b423930d-73f3-47fa-bc34-26b59bcb0694</t>
   </si>
   <si>
-    <t>18:12:56</t>
-  </si>
-  <si>
-    <t>MACARENa CATALAN BENITEZ</t>
-  </si>
-  <si>
-    <t>17.229.411-1</t>
-  </si>
-  <si>
     <t>104fa351-03cf-48da-814a-97d936274664</t>
   </si>
   <si>
-    <t>79e0a58a-afc4-48fd-8949-f8a29b6c542e</t>
-  </si>
-  <si>
-    <t>b96339ce-d0f1-4fac-b32b-66d13f0bf7a7</t>
-  </si>
-  <si>
     <t>be947024-0051-4526-a030-a7afe1f5ca05</t>
   </si>
   <si>
     <t>7e78ecb3-e31a-4899-b62e-0a0a932fc469</t>
   </si>
   <si>
+    <t>4ac7f830-7fab-4927-9b5e-f8619b8181fb</t>
+  </si>
+  <si>
+    <t>17f16576-fa36-46af-89bb-c04f8312b615</t>
+  </si>
+  <si>
+    <t>5f0d617a-cb4a-42fd-8e69-6ac6c51917ab</t>
+  </si>
+  <si>
+    <t>e7130524-9f9a-4412-85fb-bf5704679127</t>
+  </si>
+  <si>
     <t>ea4916a5-0b6e-4d08-a79f-d33accd9b77e</t>
   </si>
   <si>
     <t>8693bbb0-7bcf-46e1-87d3-7cd17ca014fd</t>
   </si>
   <si>
-    <t>4ac7f830-7fab-4927-9b5e-f8619b8181fb</t>
-  </si>
-  <si>
-    <t>17f16576-fa36-46af-89bb-c04f8312b615</t>
-  </si>
-  <si>
-    <t>5f0d617a-cb4a-42fd-8e69-6ac6c51917ab</t>
-  </si>
-  <si>
-    <t>e7130524-9f9a-4412-85fb-bf5704679127</t>
+    <t>f9728e31-d03c-4415-a571-2806ca89d345</t>
+  </si>
+  <si>
+    <t>18:20:03</t>
+  </si>
+  <si>
+    <t>Bruno Riquelme Lazcano</t>
+  </si>
+  <si>
+    <t>24.838.595-2</t>
+  </si>
+  <si>
+    <t>ec27a73e-18c5-4e4d-b9d6-2d0b0eca1aab</t>
+  </si>
+  <si>
+    <t>6e417581-4d84-458d-a308-212d845fad8a</t>
+  </si>
+  <si>
+    <t>dbd7c6a3-0e28-4889-b9a8-809132d2ad83</t>
   </si>
   <si>
     <t>6af67735-0d40-4507-a934-ba5914a64507</t>
   </si>
   <si>
-    <t>18:20:03</t>
-  </si>
-  <si>
-    <t>Bruno Riquelme Lazcano</t>
-  </si>
-  <si>
-    <t>24.838.595-2</t>
-  </si>
-  <si>
     <t>3634382a-15c9-432c-9158-b29c10f5889a</t>
   </si>
   <si>
-    <t>6e417581-4d84-458d-a308-212d845fad8a</t>
-  </si>
-  <si>
-    <t>dbd7c6a3-0e28-4889-b9a8-809132d2ad83</t>
-  </si>
-  <si>
     <t>0b384750-f1ba-4897-ae6d-6814c0f24474</t>
   </si>
   <si>
     <t>d0895e20-85cd-456c-ae01-62164957015d</t>
   </si>
   <si>
-    <t>f9728e31-d03c-4415-a571-2806ca89d345</t>
-  </si>
-  <si>
-    <t>ec27a73e-18c5-4e4d-b9d6-2d0b0eca1aab</t>
+    <t>bc53af80-1c6e-4b66-a9fc-145b058f4a5c</t>
+  </si>
+  <si>
+    <t>c4c10ad9-7beb-4698-8d51-7bb159bd5da9</t>
   </si>
   <si>
     <t>ddb0353b-1522-4425-9aa3-415b24e87a10</t>
@@ -4840,12 +4846,6 @@
     <t>e5916cb5-cd64-4b3b-ad38-12623f2b1c0b</t>
   </si>
   <si>
-    <t>bc53af80-1c6e-4b66-a9fc-145b058f4a5c</t>
-  </si>
-  <si>
-    <t>c4c10ad9-7beb-4698-8d51-7bb159bd5da9</t>
-  </si>
-  <si>
     <t>c490b1e8-6182-4b84-ae1c-92cc3e2fbd8d</t>
   </si>
   <si>
@@ -4888,81 +4888,81 @@
     <t>372b7f87-0938-4c47-b31a-dca4526801c1</t>
   </si>
   <si>
+    <t>0bde9a70-7647-4a53-83cc-b736a402d0ea</t>
+  </si>
+  <si>
+    <t>0a1b9fcf-5b3f-430d-b5b9-595f3cdffb75</t>
+  </si>
+  <si>
+    <t>05dcd137-acc7-4027-8204-161657a8d838</t>
+  </si>
+  <si>
+    <t>0f3d95f1-72cd-4ad4-bba8-2c24297021e0</t>
+  </si>
+  <si>
+    <t>00104c0d-d1d0-4a13-a4cd-bd1ffa306811</t>
+  </si>
+  <si>
+    <t>3d00a2ba-b82c-401d-8beb-9edd142544ad</t>
+  </si>
+  <si>
+    <t>166b8fed-c760-4bd9-82a0-a71ed1a1be8f</t>
+  </si>
+  <si>
+    <t>959c4e1a-02c2-4c22-9682-b9582b0f6e59</t>
+  </si>
+  <si>
+    <t>2632d466-db00-4d22-b688-e94b0e385515</t>
+  </si>
+  <si>
+    <t>2040cd82-375b-4f2c-b885-33df9b7a235e</t>
+  </si>
+  <si>
+    <t>4527bced-eeb2-4c87-889d-373cfba76333</t>
+  </si>
+  <si>
+    <t>15a75968-1552-4c96-8dff-20e6098360c2</t>
+  </si>
+  <si>
+    <t>404e4952-30de-4eeb-a0a4-87df847d5499</t>
+  </si>
+  <si>
+    <t>746b8da8-b909-4b52-acde-2d14bd2ee0a1</t>
+  </si>
+  <si>
+    <t>f1913a78-8f41-4d4e-ba08-816c91713b23</t>
+  </si>
+  <si>
+    <t>7109b630-bf2d-4cb0-9a6d-bea05bebb858</t>
+  </si>
+  <si>
     <t>e3043d66-07c4-43c6-86b7-46c2fb8a69dd</t>
   </si>
   <si>
     <t>4919ec94-4595-4c78-83c0-63b5cfae0482</t>
   </si>
   <si>
-    <t>f1913a78-8f41-4d4e-ba08-816c91713b23</t>
-  </si>
-  <si>
-    <t>7109b630-bf2d-4cb0-9a6d-bea05bebb858</t>
-  </si>
-  <si>
-    <t>0bde9a70-7647-4a53-83cc-b736a402d0ea</t>
-  </si>
-  <si>
-    <t>0a1b9fcf-5b3f-430d-b5b9-595f3cdffb75</t>
-  </si>
-  <si>
-    <t>05dcd137-acc7-4027-8204-161657a8d838</t>
-  </si>
-  <si>
-    <t>0f3d95f1-72cd-4ad4-bba8-2c24297021e0</t>
-  </si>
-  <si>
-    <t>00104c0d-d1d0-4a13-a4cd-bd1ffa306811</t>
-  </si>
-  <si>
-    <t>3d00a2ba-b82c-401d-8beb-9edd142544ad</t>
-  </si>
-  <si>
-    <t>166b8fed-c760-4bd9-82a0-a71ed1a1be8f</t>
-  </si>
-  <si>
-    <t>959c4e1a-02c2-4c22-9682-b9582b0f6e59</t>
-  </si>
-  <si>
-    <t>2632d466-db00-4d22-b688-e94b0e385515</t>
-  </si>
-  <si>
-    <t>2040cd82-375b-4f2c-b885-33df9b7a235e</t>
-  </si>
-  <si>
-    <t>4527bced-eeb2-4c87-889d-373cfba76333</t>
-  </si>
-  <si>
-    <t>15a75968-1552-4c96-8dff-20e6098360c2</t>
-  </si>
-  <si>
-    <t>404e4952-30de-4eeb-a0a4-87df847d5499</t>
-  </si>
-  <si>
-    <t>746b8da8-b909-4b52-acde-2d14bd2ee0a1</t>
+    <t>1bb2561d-5320-44bd-8fa6-a1e4a058a4d6</t>
+  </si>
+  <si>
+    <t>18:42:33</t>
+  </si>
+  <si>
+    <t>JOSE ROSALES MAUTINO</t>
+  </si>
+  <si>
+    <t>14.676.237-9</t>
+  </si>
+  <si>
+    <t>64a9f57c-bb2c-4eea-a3a7-9e75c82e072a</t>
   </si>
   <si>
     <t>71e86131-7d96-4b49-8f84-e6eb849389e1</t>
   </si>
   <si>
-    <t>18:42:33</t>
-  </si>
-  <si>
-    <t>JOSE ROSALES MAUTINO</t>
-  </si>
-  <si>
-    <t>14.676.237-9</t>
-  </si>
-  <si>
     <t>c1cebe79-f814-4f15-bb19-1f2285faeafd</t>
   </si>
   <si>
-    <t>1bb2561d-5320-44bd-8fa6-a1e4a058a4d6</t>
-  </si>
-  <si>
-    <t>64a9f57c-bb2c-4eea-a3a7-9e75c82e072a</t>
-  </si>
-  <si>
     <t>49d1ec57-92b8-4756-a050-3d7ecb6cf6be</t>
   </si>
   <si>
@@ -5023,18 +5023,24 @@
     <t>80dd871f-6cbc-406b-8e0d-a23da20256bb</t>
   </si>
   <si>
+    <t>22288b3e-7e8f-4a5e-a0f9-4ff70f921e3e</t>
+  </si>
+  <si>
+    <t>18:45:03</t>
+  </si>
+  <si>
+    <t>Carlos David Arrieta Reyes</t>
+  </si>
+  <si>
+    <t>11.838.719-8</t>
+  </si>
+  <si>
+    <t>703cdc96-efa5-470d-88b2-87d60c74e8a6</t>
+  </si>
+  <si>
     <t>2525b97c-a8c6-4769-ba5d-b84602d41a17</t>
   </si>
   <si>
-    <t>18:45:03</t>
-  </si>
-  <si>
-    <t>Carlos David Arrieta Reyes</t>
-  </si>
-  <si>
-    <t>11.838.719-8</t>
-  </si>
-  <si>
     <t>f8854817-d3ce-40cb-92af-113429f560af</t>
   </si>
   <si>
@@ -5044,48 +5050,66 @@
     <t>12538616-5e01-4a3e-ac0c-669774100b6b</t>
   </si>
   <si>
-    <t>22288b3e-7e8f-4a5e-a0f9-4ff70f921e3e</t>
-  </si>
-  <si>
-    <t>703cdc96-efa5-470d-88b2-87d60c74e8a6</t>
-  </si>
-  <si>
     <t>12599d95-bdae-4eb8-a1a6-05765c861a64</t>
   </si>
   <si>
     <t>3766aba8-d0e3-423b-8502-2c6fde8ce846</t>
   </si>
   <si>
+    <t>55bb5083-99e6-4ad8-a36c-da5385271034</t>
+  </si>
+  <si>
+    <t>738291a5-f08b-4aa2-bd57-1f0487e3fce3</t>
+  </si>
+  <si>
+    <t>6de22dba-9a39-4aa2-95ce-3cedd693d661</t>
+  </si>
+  <si>
+    <t>8d196db2-7135-4a1a-a94d-3903684315bb</t>
+  </si>
+  <si>
     <t>6c6179b0-7cce-455b-931a-e0e74c0936f3</t>
   </si>
   <si>
     <t>b2b1db18-7855-4eec-8100-fbf4e74c0630</t>
   </si>
   <si>
-    <t>6de22dba-9a39-4aa2-95ce-3cedd693d661</t>
-  </si>
-  <si>
-    <t>8d196db2-7135-4a1a-a94d-3903684315bb</t>
-  </si>
-  <si>
     <t>4aa0384d-0d2c-456d-b72c-7d0bf0af56c9</t>
   </si>
   <si>
     <t>117602d0-bb4b-4076-9b9b-f2f360e6661c</t>
   </si>
   <si>
-    <t>55bb5083-99e6-4ad8-a36c-da5385271034</t>
-  </si>
-  <si>
-    <t>738291a5-f08b-4aa2-bd57-1f0487e3fce3</t>
-  </si>
-  <si>
     <t>c19e7121-6d67-4095-b604-d96ca349f211</t>
   </si>
   <si>
     <t>25b21f15-91ce-4142-83b0-9ef75d0838f6</t>
   </si>
   <si>
+    <t>d931dca4-5faf-489f-be32-f2a4a1911334</t>
+  </si>
+  <si>
+    <t>0de7caca-d904-465d-8f0f-125201acb34c</t>
+  </si>
+  <si>
+    <t>89fb7c84-45ec-4f89-a9ba-69e7394d8b11</t>
+  </si>
+  <si>
+    <t>9dfa02a1-51c6-416e-8e72-cc3ed45be4d9</t>
+  </si>
+  <si>
+    <t>90bf9dd2-39a6-4d1f-9592-69f637b8fc09</t>
+  </si>
+  <si>
+    <t>189b0060-cf98-4be2-9de8-66bcbac50cb6</t>
+  </si>
+  <si>
+    <t>e80c9eab-f104-4bc0-85db-55aba4f24b6a</t>
+  </si>
+  <si>
+    <t>95e67b40-7868-492f-9199-4184f377f0e0</t>
+  </si>
+  <si>
     <t>f70d3a3c-ac01-4b18-8a33-7ed96453c131</t>
   </si>
   <si>
@@ -5098,30 +5122,6 @@
     <t>bc03017d-2454-4d16-9c0d-be5121b82f6b</t>
   </si>
   <si>
-    <t>e80c9eab-f104-4bc0-85db-55aba4f24b6a</t>
-  </si>
-  <si>
-    <t>95e67b40-7868-492f-9199-4184f377f0e0</t>
-  </si>
-  <si>
-    <t>d931dca4-5faf-489f-be32-f2a4a1911334</t>
-  </si>
-  <si>
-    <t>0de7caca-d904-465d-8f0f-125201acb34c</t>
-  </si>
-  <si>
-    <t>89fb7c84-45ec-4f89-a9ba-69e7394d8b11</t>
-  </si>
-  <si>
-    <t>9dfa02a1-51c6-416e-8e72-cc3ed45be4d9</t>
-  </si>
-  <si>
-    <t>90bf9dd2-39a6-4d1f-9592-69f637b8fc09</t>
-  </si>
-  <si>
-    <t>189b0060-cf98-4be2-9de8-66bcbac50cb6</t>
-  </si>
-  <si>
     <t>fa3150ad-e17f-4a14-9e57-32a4dc425cec</t>
   </si>
   <si>
@@ -5134,27 +5134,27 @@
     <t>05b515c5-3334-4410-93b9-77cc7e7eea27</t>
   </si>
   <si>
+    <t>f48bd2b7-2d29-4f09-9b42-88d9f1abc463</t>
+  </si>
+  <si>
+    <t>18:45:04</t>
+  </si>
+  <si>
+    <t>636147fa-9331-4e6e-84d1-816c7acb5f94</t>
+  </si>
+  <si>
+    <t>bd525ca4-c598-4c3a-9705-5001979f03a4</t>
+  </si>
+  <si>
+    <t>53ec6e40-57eb-4ecf-b3e6-d5ad33fe280a</t>
+  </si>
+  <si>
     <t>ac833128-4b71-4d6d-ac08-ba017def5023</t>
   </si>
   <si>
-    <t>18:45:04</t>
-  </si>
-  <si>
     <t>5424d5a1-d04c-4565-b8bb-f459c3b6c2b9</t>
   </si>
   <si>
-    <t>f48bd2b7-2d29-4f09-9b42-88d9f1abc463</t>
-  </si>
-  <si>
-    <t>636147fa-9331-4e6e-84d1-816c7acb5f94</t>
-  </si>
-  <si>
-    <t>bd525ca4-c598-4c3a-9705-5001979f03a4</t>
-  </si>
-  <si>
-    <t>53ec6e40-57eb-4ecf-b3e6-d5ad33fe280a</t>
-  </si>
-  <si>
     <t>46445d99-0e74-4a72-bddf-3aaa3e3b4b80</t>
   </si>
   <si>
@@ -5165,6 +5165,381 @@
   </si>
   <si>
     <t>1ecdbf7f-13f9-4ad1-b32f-6b2f0d13a488</t>
+  </si>
+  <si>
+    <t>1aafbd73-32ad-4bc1-ad59-23562bb77424</t>
+  </si>
+  <si>
+    <t>18:53:08</t>
+  </si>
+  <si>
+    <t>Roberto hernan Cáceres Beltrán</t>
+  </si>
+  <si>
+    <t>13.443.266-7</t>
+  </si>
+  <si>
+    <t>6da5201c-cdfc-48a1-94fc-aab90360d6d6</t>
+  </si>
+  <si>
+    <t>149faf5d-5c91-4dbf-a922-c78c6676f5ff</t>
+  </si>
+  <si>
+    <t>0201011c-75ae-41aa-8d2c-f46d42538791</t>
+  </si>
+  <si>
+    <t>0a12c159-ceff-4b50-b94c-70d006e2c099</t>
+  </si>
+  <si>
+    <t>94ff1199-9387-4e17-9072-b0f825c95ad9</t>
+  </si>
+  <si>
+    <t>6c89ef35-6438-4a9f-b8b4-e87064fc7815</t>
+  </si>
+  <si>
+    <t>661cedab-451c-4247-b8f1-04ad35adee91</t>
+  </si>
+  <si>
+    <t>6b8db0b4-7952-4d3b-b902-08f6410f07e4</t>
+  </si>
+  <si>
+    <t>92d062e1-ac86-4b79-90bb-0eac33bb6df3</t>
+  </si>
+  <si>
+    <t>cf7e0553-b695-4fdf-aee5-5daf816f819f</t>
+  </si>
+  <si>
+    <t>c13de862-41ad-4546-be24-7e49946c18a2</t>
+  </si>
+  <si>
+    <t>8d61bb45-7f21-40b6-a26a-c0815ee26b95</t>
+  </si>
+  <si>
+    <t>b0e4a6d0-1e71-46b6-99b2-cbea7d9f7c25</t>
+  </si>
+  <si>
+    <t>956d93fa-7f37-4285-8f33-fa63429ee63a</t>
+  </si>
+  <si>
+    <t>25653563-8b8a-420c-a8fc-29e60eb406f1</t>
+  </si>
+  <si>
+    <t>8ad0cdbd-110d-4ca4-8a25-28e4353f2cb4</t>
+  </si>
+  <si>
+    <t>188b4d1c-3e27-4684-a28f-fa927f5a59db</t>
+  </si>
+  <si>
+    <t>8970f125-dad7-4ed9-9647-6211635e832a</t>
+  </si>
+  <si>
+    <t>18:53:09</t>
+  </si>
+  <si>
+    <t>1591a317-f861-4d84-bbe0-448761aaacd0</t>
+  </si>
+  <si>
+    <t>820829ee-222d-4acd-905a-24ad5f64747e</t>
+  </si>
+  <si>
+    <t>038eb7cc-1fd6-46c9-a12a-194632fefbbb</t>
+  </si>
+  <si>
+    <t>6ff4c987-adea-4016-bf8c-434249be71bb</t>
+  </si>
+  <si>
+    <t>0d3b3078-f651-4a4a-a510-dacaffe95cf6</t>
+  </si>
+  <si>
+    <t>94aa9fa9-fd10-4cb8-b568-724e088bd324</t>
+  </si>
+  <si>
+    <t>c6c9ba6d-3303-4373-9017-4bc9205c7fb6</t>
+  </si>
+  <si>
+    <t>bfeea287-953b-40e0-ae22-84dc9badcb09</t>
+  </si>
+  <si>
+    <t>9243fa4f-5d73-421f-992e-62999ea19fb2</t>
+  </si>
+  <si>
+    <t>cafe3280-64af-4bb4-b40a-076ebf197ab9</t>
+  </si>
+  <si>
+    <t>d918bead-d7e5-4bde-9d31-69c2a9a76a3b</t>
+  </si>
+  <si>
+    <t>5813330e-0575-4e77-b9a6-7e241b7440b7</t>
+  </si>
+  <si>
+    <t>2042273e-2da7-41c3-b3a2-54b6d9b5d388</t>
+  </si>
+  <si>
+    <t>0bc66575-4887-4f2a-bbcd-32ab1e4918c5</t>
+  </si>
+  <si>
+    <t>d07113b7-43bd-458e-b57a-a716db391382</t>
+  </si>
+  <si>
+    <t>3251b325-8029-4e92-af59-ca63721dcc54</t>
+  </si>
+  <si>
+    <t>5974788a-0891-4150-8b83-54c3cc2b980d</t>
+  </si>
+  <si>
+    <t>27e5195f-435d-4407-af65-16a8460dc85a</t>
+  </si>
+  <si>
+    <t>680614f6-03ea-4286-99d8-76115872dc9e</t>
+  </si>
+  <si>
+    <t>a9c2035c-e9b7-4848-aa67-8bc0bbd5e61d</t>
+  </si>
+  <si>
+    <t>18:53:10</t>
+  </si>
+  <si>
+    <t>a7c72d99-3bd5-454a-865f-16a4ea811104</t>
+  </si>
+  <si>
+    <t>6fc2ef4d-9b77-4fe6-91f8-8a8eb1100e10</t>
+  </si>
+  <si>
+    <t>19:11:16</t>
+  </si>
+  <si>
+    <t>01b637cf-5e9d-42d2-8ce3-87fe16b20d7b</t>
+  </si>
+  <si>
+    <t>06b0e2f6-6ad9-4bae-9e1c-22ddbb7539fb</t>
+  </si>
+  <si>
+    <t>d36119d1-c2fd-4670-8a84-0698abcc8575</t>
+  </si>
+  <si>
+    <t>5da931a2-7ff3-4eda-ace9-9884f105f326</t>
+  </si>
+  <si>
+    <t>19:11:17</t>
+  </si>
+  <si>
+    <t>a5f88e15-cc35-464b-8a02-a033146cff37</t>
+  </si>
+  <si>
+    <t>6ade01d1-eecf-42c6-9a41-43b18a8073b2</t>
+  </si>
+  <si>
+    <t>e7477c68-2811-43e6-abad-29908ba64f8b</t>
+  </si>
+  <si>
+    <t>68b0261d-4040-4fc1-90ad-46f2455533b4</t>
+  </si>
+  <si>
+    <t>b27fb5b3-ca72-476c-a143-1f2293ce4bfa</t>
+  </si>
+  <si>
+    <t>3ea866ff-9636-400c-8630-95deb9bb6cc8</t>
+  </si>
+  <si>
+    <t>f9dfa2bd-c0d0-4519-95dd-0db8a85236a8</t>
+  </si>
+  <si>
+    <t>80384b1f-3b25-490d-93b2-e466e3948bd6</t>
+  </si>
+  <si>
+    <t>945be4c4-1f6f-4ed9-b4e6-5a4e7eaab261</t>
+  </si>
+  <si>
+    <t>862a1235-a808-49c1-8ee0-94622cb3f112</t>
+  </si>
+  <si>
+    <t>bcc32be7-a99c-4eb9-a1fe-30a3db15394d</t>
+  </si>
+  <si>
+    <t>b25e2e7a-7038-439a-8219-8d961e0842e5</t>
+  </si>
+  <si>
+    <t>c0b71928-f99a-4e1d-810c-5d421ad8ed29</t>
+  </si>
+  <si>
+    <t>c11d88cc-3316-4a14-bf06-2d8c1c28af9b</t>
+  </si>
+  <si>
+    <t>b069dcd1-5675-414b-87f7-38fd826394ae</t>
+  </si>
+  <si>
+    <t>c1b58812-64c4-41d9-b58e-bed5c7bbdf74</t>
+  </si>
+  <si>
+    <t>c9762579-9f24-4c73-b192-39f4b7e4bba7</t>
+  </si>
+  <si>
+    <t>cf4d9dc4-bc38-4a82-808e-6d3dc9e72d1c</t>
+  </si>
+  <si>
+    <t>19:11:18</t>
+  </si>
+  <si>
+    <t>08cebf43-2227-4e3a-9142-c2368bdf67f2</t>
+  </si>
+  <si>
+    <t>d0c85bbb-14cf-48c7-9681-c895b02860fd</t>
+  </si>
+  <si>
+    <t>f8dbec2a-bfa2-464a-9bb7-158906c5f36d</t>
+  </si>
+  <si>
+    <t>9990c52a-beca-4dfa-b80b-d99e6156b3da</t>
+  </si>
+  <si>
+    <t>f7c7da8e-2c6b-4202-9f9c-058b017a3b86</t>
+  </si>
+  <si>
+    <t>a2660c0b-13a6-44dd-b105-a3faa7d06288</t>
+  </si>
+  <si>
+    <t>7ef4f05d-c522-4364-b928-05c6db55abf5</t>
+  </si>
+  <si>
+    <t>58cf8606-2b6c-452f-b6c2-2ecc04eb230e</t>
+  </si>
+  <si>
+    <t>db485fa2-efd7-4b8b-ad23-248c15e68bea</t>
+  </si>
+  <si>
+    <t>02cc01b8-1b03-4adf-b1fb-3158fc9c8fcd</t>
+  </si>
+  <si>
+    <t>a741f87e-ea68-4232-a286-bf8caf8a071b</t>
+  </si>
+  <si>
+    <t>1d9f8483-55ed-4f63-badb-32c91beef134</t>
+  </si>
+  <si>
+    <t>0bf6da81-9659-45ba-a644-356f1ab5c817</t>
+  </si>
+  <si>
+    <t>8d6f6498-776f-4744-9300-4a2a3f7ad15a</t>
+  </si>
+  <si>
+    <t>19:11:19</t>
+  </si>
+  <si>
+    <t>2ee922bd-3856-4976-8dec-89124c3a4562</t>
+  </si>
+  <si>
+    <t>d7627b43-14d5-4462-b4c6-f90271c20c43</t>
+  </si>
+  <si>
+    <t>f9c4a06c-dd7b-4b6c-acea-b4b9c51e7b39</t>
+  </si>
+  <si>
+    <t>cc97baf3-03f5-4147-b23e-73ea889e4775</t>
+  </si>
+  <si>
+    <t>19:20:30</t>
+  </si>
+  <si>
+    <t>ANGELA SALINAS ARANCIBIA</t>
+  </si>
+  <si>
+    <t>15.482.362-K</t>
+  </si>
+  <si>
+    <t>03bf1216-e20d-42b9-ae33-7457359608b2</t>
+  </si>
+  <si>
+    <t>ae369637-2b29-4c03-adb8-dad85f211108</t>
+  </si>
+  <si>
+    <t>2de05eab-0763-4409-9c96-853f478e67e6</t>
+  </si>
+  <si>
+    <t>acf49846-9a4b-4cd2-aee7-86f2d491837b</t>
+  </si>
+  <si>
+    <t>e88e7efa-fe7c-4770-a846-609b10e4afaa</t>
+  </si>
+  <si>
+    <t>aabda446-56c5-45c0-a82a-cf7ee510e87b</t>
+  </si>
+  <si>
+    <t>7193dbe9-dff9-496b-81ef-9fd89c3c90e5</t>
+  </si>
+  <si>
+    <t>841db186-05b5-428f-9d76-753f28fc9991</t>
+  </si>
+  <si>
+    <t>ea650f88-6230-4f5f-af5a-6e34240e9920</t>
+  </si>
+  <si>
+    <t>29de1e78-4237-4af8-94cc-156bacc118db</t>
+  </si>
+  <si>
+    <t>194e5a5a-4d1b-4ecb-b7a0-37232129f29e</t>
+  </si>
+  <si>
+    <t>5aab32c2-db53-47ee-b9f4-ebab6ad502b0</t>
+  </si>
+  <si>
+    <t>bed5b7c5-e4e4-4363-bece-4fd68b5cfde1</t>
+  </si>
+  <si>
+    <t>27fd0774-0727-4e05-8ead-cbedbb68d9dd</t>
+  </si>
+  <si>
+    <t>19:20:31</t>
+  </si>
+  <si>
+    <t>97d1d200-da5e-416f-9455-37c2c509e460</t>
+  </si>
+  <si>
+    <t>8739b62b-d6cb-4dca-84c3-d84e29402b53</t>
+  </si>
+  <si>
+    <t>10c2bb3e-0654-4b75-bcc3-648ea88fd5a6</t>
+  </si>
+  <si>
+    <t>e8ffd9ac-1257-422e-9cb3-36cb21154104</t>
+  </si>
+  <si>
+    <t>e020ba31-b2e7-4699-a09a-86aac1a2b793</t>
+  </si>
+  <si>
+    <t>0e7af844-c7db-4734-9d62-5d25b07a3a95</t>
+  </si>
+  <si>
+    <t>19:48:28</t>
+  </si>
+  <si>
+    <t>Logoff</t>
+  </si>
+  <si>
+    <t>ad94ff71-dda5-4158-9613-0d5f6dabb648</t>
+  </si>
+  <si>
+    <t>19:55:15</t>
+  </si>
+  <si>
+    <t>c0f4d68b-b0e8-46af-b1fa-caac39ce1280</t>
+  </si>
+  <si>
+    <t>19:55:38</t>
+  </si>
+  <si>
+    <t>0063a8a3-be4e-4c14-bfa4-844fe9dc6bbd</t>
+  </si>
+  <si>
+    <t>807d5c00-616f-47dd-bbf9-19b76ccddc76</t>
+  </si>
+  <si>
+    <t>19:57:13</t>
+  </si>
+  <si>
+    <t>604d737f-b96a-4f5a-9169-3a99224e46c2</t>
+  </si>
+  <si>
+    <t>19:57:34</t>
   </si>
 </sst>
 </file>
@@ -5217,8 +5592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:L593" totalsRowShown="0">
-  <autoFilter ref="A1:L593"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:L649" totalsRowShown="0">
+  <autoFilter ref="A1:L649"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID" dataDxfId="0"/>
     <tableColumn id="2" name="Fecha" dataDxfId="0"/>
@@ -5522,7 +5897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L593"/>
+  <dimension ref="A1:L649"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -27928,6 +28303,2074 @@
       <c r="L593" s="1" t="s">
         <v>1716</v>
       </c>
+    </row>
+    <row r="594" spans="1:12">
+      <c r="A594" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D594" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F594" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G594" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H594" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I594" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J594" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K594" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L594" s="1" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="595" spans="1:12">
+      <c r="A595" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F595" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G595" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H595" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I595" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J595" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K595" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L595" s="1" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="596" spans="1:12">
+      <c r="A596" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G596" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H596" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I596" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J596" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K596" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L596" s="1" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="597" spans="1:12">
+      <c r="A597" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F597" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H597" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I597" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J597" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K597" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L597" s="1" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="598" spans="1:12">
+      <c r="A598" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F598" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H598" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I598" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J598" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K598" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L598" s="1" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="599" spans="1:12">
+      <c r="A599" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F599" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H599" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I599" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J599" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K599" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L599" s="1" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="600" spans="1:12">
+      <c r="A600" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F600" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G600" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H600" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I600" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J600" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K600" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L600" s="1" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="601" spans="1:12">
+      <c r="A601" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G601" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H601" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I601" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J601" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K601" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L601" s="1" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="602" spans="1:12">
+      <c r="A602" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F602" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G602" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H602" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I602" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J602" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K602" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L602" s="1" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="603" spans="1:12">
+      <c r="A603" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F603" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G603" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H603" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I603" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J603" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K603" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L603" s="1" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="604" spans="1:12">
+      <c r="A604" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F604" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G604" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H604" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J604" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K604" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L604" s="1" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="605" spans="1:12">
+      <c r="A605" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H605" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I605" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J605" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K605" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L605" s="1" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="606" spans="1:12">
+      <c r="A606" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G606" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H606" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I606" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J606" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K606" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L606" s="1" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="607" spans="1:12">
+      <c r="A607" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F607" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G607" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H607" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I607" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J607" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K607" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L607" s="1" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="608" spans="1:12">
+      <c r="A608" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F608" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G608" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H608" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I608" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J608" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K608" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L608" s="1" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="609" spans="1:12">
+      <c r="A609" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F609" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G609" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H609" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I609" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J609" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K609" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L609" s="1" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="610" spans="1:12">
+      <c r="A610" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G610" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H610" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I610" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J610" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K610" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L610" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="611" spans="1:12">
+      <c r="A611" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F611" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G611" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H611" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I611" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J611" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K611" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L611" s="1" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="612" spans="1:12">
+      <c r="A612" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F612" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G612" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H612" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I612" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J612" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K612" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L612" s="1" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="613" spans="1:12">
+      <c r="A613" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G613" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H613" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I613" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J613" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K613" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L613" s="1" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="614" spans="1:12">
+      <c r="A614" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F614" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G614" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H614" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I614" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J614" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K614" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L614" s="1" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="615" spans="1:12">
+      <c r="A615" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F615" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G615" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H615" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I615" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J615" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K615" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L615" s="1" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="616" spans="1:12">
+      <c r="A616" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G616" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H616" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I616" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J616" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K616" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L616" s="1" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="617" spans="1:12">
+      <c r="A617" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F617" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H617" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I617" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J617" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K617" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L617" s="1" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="618" spans="1:12">
+      <c r="A618" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F618" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G618" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H618" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I618" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J618" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K618" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L618" s="1" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="619" spans="1:12">
+      <c r="A619" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F619" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G619" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H619" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I619" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J619" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K619" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L619" s="1" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="620" spans="1:12">
+      <c r="A620" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G620" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H620" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I620" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J620" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K620" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L620" s="1" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="621" spans="1:12">
+      <c r="A621" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F621" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G621" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H621" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I621" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J621" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K621" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L621" s="1" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="622" spans="1:12">
+      <c r="A622" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F622" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G622" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H622" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I622" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J622" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K622" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L622" s="1" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="623" spans="1:12">
+      <c r="A623" s="1" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G623" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H623" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I623" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J623" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K623" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L623" s="1" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="624" spans="1:12">
+      <c r="A624" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G624" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H624" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I624" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J624" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K624" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L624" s="1" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="625" spans="1:12">
+      <c r="A625" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F625" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G625" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H625" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I625" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J625" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K625" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L625" s="1" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="626" spans="1:12">
+      <c r="A626" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F626" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G626" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H626" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I626" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J626" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K626" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L626" s="1" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="627" spans="1:12">
+      <c r="A627" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G627" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H627" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I627" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J627" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K627" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L627" s="1" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="628" spans="1:12">
+      <c r="A628" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G628" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H628" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I628" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J628" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K628" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L628" s="1" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="629" spans="1:12">
+      <c r="A629" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G629" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H629" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I629" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J629" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K629" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L629" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="630" spans="1:12">
+      <c r="A630" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G630" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H630" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I630" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J630" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K630" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L630" s="1" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="631" spans="1:12">
+      <c r="A631" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F631" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G631" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H631" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I631" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J631" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K631" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L631" s="1" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="632" spans="1:12">
+      <c r="A632" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G632" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H632" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I632" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J632" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K632" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L632" s="1" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="633" spans="1:12">
+      <c r="A633" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G633" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H633" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="I633" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J633" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K633" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L633" s="1" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="634" spans="1:12">
+      <c r="A634" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G634" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H634" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I634" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J634" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K634" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L634" s="1" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="635" spans="1:12">
+      <c r="A635" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F635" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G635" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H635" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I635" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J635" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K635" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L635" s="1" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="636" spans="1:12">
+      <c r="A636" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F636" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G636" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H636" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I636" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J636" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K636" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L636" s="1" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="637" spans="1:12">
+      <c r="A637" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F637" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G637" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H637" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I637" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J637" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K637" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L637" s="1" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="638" spans="1:12">
+      <c r="A638" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G638" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H638" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I638" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J638" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K638" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L638" s="1" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="639" spans="1:12">
+      <c r="A639" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G639" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H639" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I639" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J639" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K639" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L639" s="1" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="640" spans="1:12">
+      <c r="A640" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F640" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G640" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H640" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I640" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J640" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K640" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L640" s="1" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="641" spans="1:12">
+      <c r="A641" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F641" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G641" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H641" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I641" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J641" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K641" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L641" s="1" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="642" spans="1:12">
+      <c r="A642" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F642" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G642" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H642" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I642" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J642" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K642" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L642" s="1" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="643" spans="1:12">
+      <c r="A643" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G643" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H643" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I643" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J643" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K643" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L643" s="1" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="644" spans="1:12">
+      <c r="A644" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G644" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H644" s="1"/>
+      <c r="I644" s="1"/>
+      <c r="J644" s="1"/>
+      <c r="K644" s="1"/>
+      <c r="L644" s="1"/>
+    </row>
+    <row r="645" spans="1:12">
+      <c r="A645" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G645" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H645" s="1"/>
+      <c r="I645" s="1"/>
+      <c r="J645" s="1"/>
+      <c r="K645" s="1"/>
+      <c r="L645" s="1"/>
+    </row>
+    <row r="646" spans="1:12">
+      <c r="A646" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G646" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H646" s="1"/>
+      <c r="I646" s="1"/>
+      <c r="J646" s="1"/>
+      <c r="K646" s="1"/>
+      <c r="L646" s="1"/>
+    </row>
+    <row r="647" spans="1:12">
+      <c r="A647" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G647" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H647" s="1"/>
+      <c r="I647" s="1"/>
+      <c r="J647" s="1"/>
+      <c r="K647" s="1"/>
+      <c r="L647" s="1"/>
+    </row>
+    <row r="648" spans="1:12">
+      <c r="A648" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G648" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H648" s="1"/>
+      <c r="I648" s="1"/>
+      <c r="J648" s="1"/>
+      <c r="K648" s="1"/>
+      <c r="L648" s="1"/>
+    </row>
+    <row r="649" spans="1:12">
+      <c r="A649" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G649" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H649" s="1"/>
+      <c r="I649" s="1"/>
+      <c r="J649" s="1"/>
+      <c r="K649" s="1"/>
+      <c r="L649" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
